--- a/artfynd/A 52891-2024 artfynd.xlsx
+++ b/artfynd/A 52891-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589827</v>
+        <v>121589821</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650512</v>
+        <v>650607</v>
       </c>
       <c r="R3" t="n">
-        <v>7170960</v>
+        <v>7170753</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589826</v>
+        <v>121589825</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650509</v>
+        <v>650530</v>
       </c>
       <c r="R4" t="n">
-        <v>7170935</v>
+        <v>7170842</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589822</v>
+        <v>121589827</v>
       </c>
       <c r="B5" t="n">
-        <v>79725</v>
+        <v>90738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650583</v>
+        <v>650512</v>
       </c>
       <c r="R5" t="n">
-        <v>7170840</v>
+        <v>7170960</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589821</v>
+        <v>121589826</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650607</v>
+        <v>650509</v>
       </c>
       <c r="R6" t="n">
-        <v>7170753</v>
+        <v>7170935</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589825</v>
+        <v>121589824</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650530</v>
+        <v>650562</v>
       </c>
       <c r="R7" t="n">
-        <v>7170842</v>
+        <v>7170836</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589824</v>
+        <v>121589822</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>79725</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,20 +1328,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650562</v>
+        <v>650583</v>
       </c>
       <c r="R8" t="n">
-        <v>7170836</v>
+        <v>7170840</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 52891-2024 artfynd.xlsx
+++ b/artfynd/A 52891-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589823</v>
+        <v>121589822</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>79725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -755,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer på grov sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589821</v>
+        <v>121589826</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -830,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650607</v>
+        <v>650509</v>
       </c>
       <c r="R3" t="n">
-        <v>7170753</v>
+        <v>7170935</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589825</v>
+        <v>121589823</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650530</v>
+        <v>650583</v>
       </c>
       <c r="R4" t="n">
-        <v>7170842</v>
+        <v>7170840</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växer på grov sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589827</v>
+        <v>121589821</v>
       </c>
       <c r="B5" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650512</v>
+        <v>650607</v>
       </c>
       <c r="R5" t="n">
-        <v>7170960</v>
+        <v>7170753</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589826</v>
+        <v>121589824</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650509</v>
+        <v>650562</v>
       </c>
       <c r="R6" t="n">
-        <v>7170935</v>
+        <v>7170836</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589824</v>
+        <v>121589825</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650562</v>
+        <v>650530</v>
       </c>
       <c r="R7" t="n">
-        <v>7170836</v>
+        <v>7170842</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589822</v>
+        <v>121589827</v>
       </c>
       <c r="B8" t="n">
-        <v>79725</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650583</v>
+        <v>650512</v>
       </c>
       <c r="R8" t="n">
-        <v>7170840</v>
+        <v>7170960</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 52891-2024 artfynd.xlsx
+++ b/artfynd/A 52891-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589823</v>
+        <v>121589824</v>
       </c>
       <c r="B4" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650583</v>
+        <v>650562</v>
       </c>
       <c r="R4" t="n">
-        <v>7170840</v>
+        <v>7170836</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,11 +967,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växer på grov sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589821</v>
+        <v>121589823</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650607</v>
+        <v>650583</v>
       </c>
       <c r="R5" t="n">
-        <v>7170753</v>
+        <v>7170840</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på grov sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589824</v>
+        <v>121589821</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650562</v>
+        <v>650607</v>
       </c>
       <c r="R6" t="n">
-        <v>7170836</v>
+        <v>7170753</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 52891-2024 artfynd.xlsx
+++ b/artfynd/A 52891-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121589822</v>
       </c>
       <c r="B2" t="n">
-        <v>79725</v>
+        <v>79732</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589826</v>
+        <v>121589827</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650509</v>
+        <v>650512</v>
       </c>
       <c r="R3" t="n">
-        <v>7170935</v>
+        <v>7170960</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589824</v>
+        <v>121589825</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650562</v>
+        <v>650530</v>
       </c>
       <c r="R4" t="n">
-        <v>7170836</v>
+        <v>7170842</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,7 +996,7 @@
         <v>121589823</v>
       </c>
       <c r="B5" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589821</v>
+        <v>121589824</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650607</v>
+        <v>650562</v>
       </c>
       <c r="R6" t="n">
-        <v>7170753</v>
+        <v>7170836</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589825</v>
+        <v>121589821</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650530</v>
+        <v>650607</v>
       </c>
       <c r="R7" t="n">
-        <v>7170842</v>
+        <v>7170753</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589827</v>
+        <v>121589826</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650512</v>
+        <v>650509</v>
       </c>
       <c r="R8" t="n">
-        <v>7170960</v>
+        <v>7170935</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 52891-2024 artfynd.xlsx
+++ b/artfynd/A 52891-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589821</v>
+        <v>121589826</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650607</v>
+        <v>650509</v>
       </c>
       <c r="R2" t="n">
-        <v>7170753</v>
+        <v>7170935</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589822</v>
+        <v>121589824</v>
       </c>
       <c r="B4" t="n">
-        <v>79732</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,20 +899,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650583</v>
+        <v>650562</v>
       </c>
       <c r="R4" t="n">
-        <v>7170840</v>
+        <v>7170836</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589827</v>
+        <v>121589823</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>79697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650512</v>
+        <v>650583</v>
       </c>
       <c r="R5" t="n">
-        <v>7170960</v>
+        <v>7170840</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1073,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på grov sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589826</v>
+        <v>121589822</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>79732</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,20 +1116,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1143,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650509</v>
+        <v>650583</v>
       </c>
       <c r="R6" t="n">
-        <v>7170935</v>
+        <v>7170840</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589824</v>
+        <v>121589827</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650562</v>
+        <v>650512</v>
       </c>
       <c r="R7" t="n">
-        <v>7170836</v>
+        <v>7170960</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589823</v>
+        <v>121589821</v>
       </c>
       <c r="B8" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650583</v>
+        <v>650607</v>
       </c>
       <c r="R8" t="n">
-        <v>7170840</v>
+        <v>7170753</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1391,11 +1396,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer på grov sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 52891-2024 artfynd.xlsx
+++ b/artfynd/A 52891-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589826</v>
+        <v>121589821</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650509</v>
+        <v>650607</v>
       </c>
       <c r="R2" t="n">
-        <v>7170935</v>
+        <v>7170753</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589825</v>
+        <v>121589827</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650530</v>
+        <v>650512</v>
       </c>
       <c r="R3" t="n">
-        <v>7170842</v>
+        <v>7170960</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589824</v>
+        <v>121589823</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650562</v>
+        <v>650583</v>
       </c>
       <c r="R4" t="n">
-        <v>7170836</v>
+        <v>7170840</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växer på grov sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589823</v>
+        <v>121589825</v>
       </c>
       <c r="B5" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650583</v>
+        <v>650530</v>
       </c>
       <c r="R5" t="n">
-        <v>7170840</v>
+        <v>7170842</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1073,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer på grov sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589822</v>
+        <v>121589826</v>
       </c>
       <c r="B6" t="n">
-        <v>79732</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,20 +1116,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650583</v>
+        <v>650509</v>
       </c>
       <c r="R6" t="n">
-        <v>7170840</v>
+        <v>7170935</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589827</v>
+        <v>121589824</v>
       </c>
       <c r="B7" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650512</v>
+        <v>650562</v>
       </c>
       <c r="R7" t="n">
-        <v>7170960</v>
+        <v>7170836</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589821</v>
+        <v>121589822</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>79732</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,20 +1328,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650607</v>
+        <v>650583</v>
       </c>
       <c r="R8" t="n">
-        <v>7170753</v>
+        <v>7170840</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 52891-2024 artfynd.xlsx
+++ b/artfynd/A 52891-2024 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589824</v>
+        <v>121589821</v>
       </c>
       <c r="B2" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650562</v>
+        <v>650607</v>
       </c>
       <c r="R2" t="n">
-        <v>7170836</v>
+        <v>7170753</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589827</v>
+        <v>121589824</v>
       </c>
       <c r="B3" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650512</v>
+        <v>650562</v>
       </c>
       <c r="R3" t="n">
-        <v>7170960</v>
+        <v>7170836</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589823</v>
+        <v>121589825</v>
       </c>
       <c r="B4" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650583</v>
+        <v>650530</v>
       </c>
       <c r="R4" t="n">
-        <v>7170840</v>
+        <v>7170842</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,11 +952,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växer på grov sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,19 +978,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589821</v>
+        <v>121589826</v>
       </c>
       <c r="B5" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1042,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650607</v>
+        <v>650509</v>
       </c>
       <c r="R5" t="n">
-        <v>7170753</v>
+        <v>7170935</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,32 +1079,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589822</v>
+        <v>121589828</v>
       </c>
       <c r="B6" t="n">
-        <v>79745</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1148,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650583</v>
+        <v>650645</v>
       </c>
       <c r="R6" t="n">
-        <v>7170840</v>
+        <v>7170985</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589825</v>
+        <v>121589823</v>
       </c>
       <c r="B7" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1254,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650530</v>
+        <v>650583</v>
       </c>
       <c r="R7" t="n">
-        <v>7170842</v>
+        <v>7170840</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1290,6 +1255,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer på grov sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,32 +1286,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589826</v>
+        <v>121589822</v>
       </c>
       <c r="B8" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1360,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650509</v>
+        <v>650583</v>
       </c>
       <c r="R8" t="n">
-        <v>7170935</v>
+        <v>7170840</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 52891-2024 artfynd.xlsx
+++ b/artfynd/A 52891-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589821</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589824</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589825</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589826</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589828</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589823</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,8 +1419,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589822</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>